--- a/datasets/dataset1.xlsx
+++ b/datasets/dataset1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mohamedelawadi/Documents/HNU/Second year/SECOND TERM/AI/vrp-PAC-MAN-edition/datasets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mohamedelawadi/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D7C0C84-10D6-5546-8261-9B0739E5663A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D02C99B-E4AC-3A44-90AF-2311C7DB9272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="206">
   <si>
     <t>Customer_ID</t>
   </si>
@@ -65,13 +65,586 @@
   </si>
   <si>
     <t>C10</t>
+  </si>
+  <si>
+    <t>C11</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>C13</t>
+  </si>
+  <si>
+    <t>C14</t>
+  </si>
+  <si>
+    <t>C15</t>
+  </si>
+  <si>
+    <t>C16</t>
+  </si>
+  <si>
+    <t>C17</t>
+  </si>
+  <si>
+    <t>C18</t>
+  </si>
+  <si>
+    <t>C19</t>
+  </si>
+  <si>
+    <t>C20</t>
+  </si>
+  <si>
+    <t>C21</t>
+  </si>
+  <si>
+    <t>C22</t>
+  </si>
+  <si>
+    <t>C23</t>
+  </si>
+  <si>
+    <t>C24</t>
+  </si>
+  <si>
+    <t>C25</t>
+  </si>
+  <si>
+    <t>C26</t>
+  </si>
+  <si>
+    <t>C27</t>
+  </si>
+  <si>
+    <t>C28</t>
+  </si>
+  <si>
+    <t>C29</t>
+  </si>
+  <si>
+    <t>C30</t>
+  </si>
+  <si>
+    <t>C31</t>
+  </si>
+  <si>
+    <t>C32</t>
+  </si>
+  <si>
+    <t>C33</t>
+  </si>
+  <si>
+    <t>C34</t>
+  </si>
+  <si>
+    <t>C35</t>
+  </si>
+  <si>
+    <t>C36</t>
+  </si>
+  <si>
+    <t>C37</t>
+  </si>
+  <si>
+    <t>C38</t>
+  </si>
+  <si>
+    <t>C39</t>
+  </si>
+  <si>
+    <t>C40</t>
+  </si>
+  <si>
+    <t>C41</t>
+  </si>
+  <si>
+    <t>C42</t>
+  </si>
+  <si>
+    <t>C43</t>
+  </si>
+  <si>
+    <t>C44</t>
+  </si>
+  <si>
+    <t>C45</t>
+  </si>
+  <si>
+    <t>C46</t>
+  </si>
+  <si>
+    <t>C47</t>
+  </si>
+  <si>
+    <t>C48</t>
+  </si>
+  <si>
+    <t>C49</t>
+  </si>
+  <si>
+    <t>C50</t>
+  </si>
+  <si>
+    <t>C51</t>
+  </si>
+  <si>
+    <t>C52</t>
+  </si>
+  <si>
+    <t>C53</t>
+  </si>
+  <si>
+    <t>C54</t>
+  </si>
+  <si>
+    <t>C55</t>
+  </si>
+  <si>
+    <t>C56</t>
+  </si>
+  <si>
+    <t>C57</t>
+  </si>
+  <si>
+    <t>C58</t>
+  </si>
+  <si>
+    <t>C59</t>
+  </si>
+  <si>
+    <t>C60</t>
+  </si>
+  <si>
+    <t>C61</t>
+  </si>
+  <si>
+    <t>C62</t>
+  </si>
+  <si>
+    <t>C63</t>
+  </si>
+  <si>
+    <t>C64</t>
+  </si>
+  <si>
+    <t>C65</t>
+  </si>
+  <si>
+    <t>C66</t>
+  </si>
+  <si>
+    <t>C67</t>
+  </si>
+  <si>
+    <t>C68</t>
+  </si>
+  <si>
+    <t>C69</t>
+  </si>
+  <si>
+    <t>C70</t>
+  </si>
+  <si>
+    <t>C71</t>
+  </si>
+  <si>
+    <t>C72</t>
+  </si>
+  <si>
+    <t>C73</t>
+  </si>
+  <si>
+    <t>C74</t>
+  </si>
+  <si>
+    <t>C75</t>
+  </si>
+  <si>
+    <t>C76</t>
+  </si>
+  <si>
+    <t>C77</t>
+  </si>
+  <si>
+    <t>C78</t>
+  </si>
+  <si>
+    <t>C79</t>
+  </si>
+  <si>
+    <t>C80</t>
+  </si>
+  <si>
+    <t>C81</t>
+  </si>
+  <si>
+    <t>C82</t>
+  </si>
+  <si>
+    <t>C83</t>
+  </si>
+  <si>
+    <t>C84</t>
+  </si>
+  <si>
+    <t>C85</t>
+  </si>
+  <si>
+    <t>C86</t>
+  </si>
+  <si>
+    <t>C87</t>
+  </si>
+  <si>
+    <t>C88</t>
+  </si>
+  <si>
+    <t>C89</t>
+  </si>
+  <si>
+    <t>C90</t>
+  </si>
+  <si>
+    <t>C91</t>
+  </si>
+  <si>
+    <t>C92</t>
+  </si>
+  <si>
+    <t>C93</t>
+  </si>
+  <si>
+    <t>C94</t>
+  </si>
+  <si>
+    <t>C95</t>
+  </si>
+  <si>
+    <t>C96</t>
+  </si>
+  <si>
+    <t>C97</t>
+  </si>
+  <si>
+    <t>C98</t>
+  </si>
+  <si>
+    <t>C99</t>
+  </si>
+  <si>
+    <t>C100</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>163 Gezira Street, Garden City, Cairo</t>
+  </si>
+  <si>
+    <t>95 Syria Street, Mohandessin, Cairo</t>
+  </si>
+  <si>
+    <t>172 Corniche El Nil, Madinaty, Cairo</t>
+  </si>
+  <si>
+    <t>240 Gameat El Dewal Street, Heliopolis, Cairo</t>
+  </si>
+  <si>
+    <t>19 Mossadak Street, Heliopolis, Cairo</t>
+  </si>
+  <si>
+    <t>44 Mohamed Mazhar Street, Zamalek, Cairo</t>
+  </si>
+  <si>
+    <t>63 Champollion Street, Sayeda Zeinab, Cairo</t>
+  </si>
+  <si>
+    <t>98 Corniche El Nil, Heliopolis, Cairo</t>
+  </si>
+  <si>
+    <t>177 Makram Ebeid Street, Sheikh Zayed City, Cairo</t>
+  </si>
+  <si>
+    <t>176 Hegaz Street, Ain Shams, Cairo</t>
+  </si>
+  <si>
+    <t>59 El Geish Street, Downtown, Cairo</t>
+  </si>
+  <si>
+    <t>103 Corniche El Nil, Dokki, Cairo</t>
+  </si>
+  <si>
+    <t>55 Adly Street, Madinaty, Cairo</t>
+  </si>
+  <si>
+    <t>81 El Khalifa El Maamoun Street, Heliopolis, Cairo</t>
+  </si>
+  <si>
+    <t>128 Ahmed Fakhry Street, Heliopolis, Cairo</t>
+  </si>
+  <si>
+    <t>118 26th of July Street, Nasr City, Cairo</t>
+  </si>
+  <si>
+    <t>36 Road 256, Zamalek, Cairo</t>
+  </si>
+  <si>
+    <t>144 Mohamed Mazhar Street, Nasr City, Cairo</t>
+  </si>
+  <si>
+    <t>192 Shehab Street, El Mokattam, Cairo</t>
+  </si>
+  <si>
+    <t>230 Shehab Street, El Manial, Cairo</t>
+  </si>
+  <si>
+    <t>93 Ramses Street, New Cairo, Cairo</t>
+  </si>
+  <si>
+    <t>131 Sherif Street, Dokki, Cairo</t>
+  </si>
+  <si>
+    <t>194 Salah Salem Street, El Sayeda Aisha, Cairo</t>
+  </si>
+  <si>
+    <t>40 Baghdad Street, Garden City, Cairo</t>
+  </si>
+  <si>
+    <t>203 Gameat El Dewal Street, El Mokattam, Cairo</t>
+  </si>
+  <si>
+    <t>153 Saraya El Gezira Street, El Manial, Cairo</t>
+  </si>
+  <si>
+    <t>98 Mossadak Street, Sayeda Zeinab, Cairo</t>
+  </si>
+  <si>
+    <t>136 El Marghany Street, Abdeen, Cairo</t>
+  </si>
+  <si>
+    <t>221 26 July Corridor, El Marg, Cairo</t>
+  </si>
+  <si>
+    <t>185 Port Said Street, El Marg, Cairo</t>
+  </si>
+  <si>
+    <t>227 Mohamed Mazhar Street, Nasr City, Cairo</t>
+  </si>
+  <si>
+    <t>197 Hassan Sabry Street, Downtown, Cairo</t>
+  </si>
+  <si>
+    <t>29 Abou Bakr El Seddik Street, El Mokattam, Cairo</t>
+  </si>
+  <si>
+    <t>41 El Tayaran Street, Agouza, Cairo</t>
+  </si>
+  <si>
+    <t>245 El Marghany Street, Shubra, Cairo</t>
+  </si>
+  <si>
+    <t>196 Abbas El Akkad Street, Shubra, Cairo</t>
+  </si>
+  <si>
+    <t>234 Zahraa El Maadi Street, Heliopolis, Cairo</t>
+  </si>
+  <si>
+    <t>77 Baghdad Street, Shubra, Cairo</t>
+  </si>
+  <si>
+    <t>156 Yousef Abbas Street, New Cairo, Cairo</t>
+  </si>
+  <si>
+    <t>96 Champollion Street, Abdeen, Cairo</t>
+  </si>
+  <si>
+    <t>245 Qasr El Nil Street, Agouza, Cairo</t>
+  </si>
+  <si>
+    <t>154 Hegaz Street, 6th of October City, Cairo</t>
+  </si>
+  <si>
+    <t>5 Port Said Street, El Matareya, Cairo</t>
+  </si>
+  <si>
+    <t>225 Road 9, Sheikh Zayed City, Cairo</t>
+  </si>
+  <si>
+    <t>15 Road 256, Maadi, Cairo</t>
+  </si>
+  <si>
+    <t>243 El Nasr Street, Dokki, Cairo</t>
+  </si>
+  <si>
+    <t>188 Sherif Street, Dokki, Cairo</t>
+  </si>
+  <si>
+    <t>195 Mohamed Mazhar Street, New Cairo, Cairo</t>
+  </si>
+  <si>
+    <t>33 Talaat Harb Street, 6th of October City, Cairo</t>
+  </si>
+  <si>
+    <t>243 Makram Ebeid Street, Garden City, Cairo</t>
+  </si>
+  <si>
+    <t>68 Qasr El Nil Street, Helwan, Cairo</t>
+  </si>
+  <si>
+    <t>109 El Khalifa El Maamoun Street, Abdeen, Cairo</t>
+  </si>
+  <si>
+    <t>194 Ahmed Orabi Street, Mohandessin, Cairo</t>
+  </si>
+  <si>
+    <t>183 Road 9, El Manial, Cairo</t>
+  </si>
+  <si>
+    <t>172 Hassan Sabry Street, El Matareya, Cairo</t>
+  </si>
+  <si>
+    <t>113 Qasr El Nil Street, Sayeda Zeinab, Cairo</t>
+  </si>
+  <si>
+    <t>31 Road 256, Sheikh Zayed City, Cairo</t>
+  </si>
+  <si>
+    <t>17 Othman Ibn Affan Street, Agouza, Cairo</t>
+  </si>
+  <si>
+    <t>151 Makram Ebeid Street, Sheikh Zayed City, Cairo</t>
+  </si>
+  <si>
+    <t>151 Ramses Street, Agouza, Cairo</t>
+  </si>
+  <si>
+    <t>19 Baghdad Street, Ain Shams, Cairo</t>
+  </si>
+  <si>
+    <t>59 Saraya El Gezira Street, Ain Shams, Cairo</t>
+  </si>
+  <si>
+    <t>221 Othman Ibn Affan Street, Dokki, Cairo</t>
+  </si>
+  <si>
+    <t>132 Road 256, Nasr City, Cairo</t>
+  </si>
+  <si>
+    <t>172 Sherif Street, Mohandessin, Cairo</t>
+  </si>
+  <si>
+    <t>139 El Thawra Street, Zamalek, Cairo</t>
+  </si>
+  <si>
+    <t>240 Adly Street, Maadi, Cairo</t>
+  </si>
+  <si>
+    <t>122 Road 256, 6th of October City, Cairo</t>
+  </si>
+  <si>
+    <t>207 Tahrir Square, Mohandessin, Cairo</t>
+  </si>
+  <si>
+    <t>25 Zahraa El Maadi Street, El Marg, Cairo</t>
+  </si>
+  <si>
+    <t>111 Syria Street, El Mokattam, Cairo</t>
+  </si>
+  <si>
+    <t>106 El Tayaran Street, Zamalek, Cairo</t>
+  </si>
+  <si>
+    <t>14 Gameat El Dewal Street, Heliopolis, Cairo</t>
+  </si>
+  <si>
+    <t>166 Zahraa El Maadi Street, Ain Shams, Cairo</t>
+  </si>
+  <si>
+    <t>104 Othman Ibn Affan Street, El Sayeda Aisha, Cairo</t>
+  </si>
+  <si>
+    <t>64 Yousef Abbas Street, Mohandessin, Cairo</t>
+  </si>
+  <si>
+    <t>138 Brazil Street, New Cairo, Cairo</t>
+  </si>
+  <si>
+    <t>109 Abbas El Akkad Street, Nasr City, Cairo</t>
+  </si>
+  <si>
+    <t>119 Road 256, Dokki, Cairo</t>
+  </si>
+  <si>
+    <t>114 Makram Ebeid Street, El Sayeda Aisha, Cairo</t>
+  </si>
+  <si>
+    <t>13 Hassan Sabry Street, Abdeen, Cairo</t>
+  </si>
+  <si>
+    <t>215 26 July Corridor, Dokki, Cairo</t>
+  </si>
+  <si>
+    <t>238 Road 256, Garden City, Cairo</t>
+  </si>
+  <si>
+    <t>105 Sherif Street, 6th of October City, Cairo</t>
+  </si>
+  <si>
+    <t>55 Ahmed Fakhry Street, Ain Shams, Cairo</t>
+  </si>
+  <si>
+    <t>43 Road 199, Agouza, Cairo</t>
+  </si>
+  <si>
+    <t>100 El Marghany Street, Sayeda Zeinab, Cairo</t>
+  </si>
+  <si>
+    <t>74 Abu El Feda Street, Madinaty, Cairo</t>
+  </si>
+  <si>
+    <t>246 Makram Ebeid Street, El Marg, Cairo</t>
+  </si>
+  <si>
+    <t>184 Sherif Street, New Cairo, Cairo</t>
+  </si>
+  <si>
+    <t>49 Abou Bakr El Seddik Street, Mohandessin, Cairo</t>
+  </si>
+  <si>
+    <t>248 Salah Salem Street, Maadi, Cairo</t>
+  </si>
+  <si>
+    <t>189 Mohamed Mazhar Street, Ain Shams, Cairo</t>
+  </si>
+  <si>
+    <t>192 Hegaz Street, Ain Shams, Cairo</t>
+  </si>
+  <si>
+    <t>13 Shehab Street, 6th of October City, Cairo</t>
+  </si>
+  <si>
+    <t>129 Qasr El Nil Street, Garden City, Cairo</t>
+  </si>
+  <si>
+    <t>15 Mostafa El Nahas Street, Dokki, Cairo</t>
+  </si>
+  <si>
+    <t>218 Abbas El Akkad Street, Dokki, Cairo</t>
+  </si>
+  <si>
+    <t>153 Saraya El Gezira Street, El Marg, Cairo</t>
+  </si>
+  <si>
+    <t>221 Road 256, El Manial, Cairo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -87,16 +660,33 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -119,14 +709,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -466,10 +1078,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:I102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -482,11 +1094,15 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -499,8 +1115,15 @@
       <c r="D2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E2" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -513,8 +1136,15 @@
       <c r="D3">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E3" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -527,8 +1157,15 @@
       <c r="D4">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E4" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -541,8 +1178,15 @@
       <c r="D5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E5" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -555,8 +1199,15 @@
       <c r="D6">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E6" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -569,8 +1220,15 @@
       <c r="D7">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E7" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -583,8 +1241,15 @@
       <c r="D8">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E8" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -597,8 +1262,15 @@
       <c r="D9">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E9" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -611,8 +1283,15 @@
       <c r="D10">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E10" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -625,8 +1304,15 @@
       <c r="D11">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E11" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -639,8 +1325,2008 @@
       <c r="D12">
         <v>17</v>
       </c>
+      <c r="E12" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13">
+        <v>87</v>
+      </c>
+      <c r="C13">
+        <v>8</v>
+      </c>
+      <c r="D13">
+        <v>12</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14">
+        <v>99</v>
+      </c>
+      <c r="C14">
+        <v>87</v>
+      </c>
+      <c r="D14">
+        <v>7</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15">
+        <v>23</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16">
+        <v>7</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17">
+        <v>21</v>
+      </c>
+      <c r="C17">
+        <v>87</v>
+      </c>
+      <c r="D17">
+        <v>17</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18">
+        <v>52</v>
+      </c>
+      <c r="C18">
+        <v>62</v>
+      </c>
+      <c r="D18">
+        <v>5</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>10</v>
+      </c>
+      <c r="D19">
+        <v>17</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20">
+        <v>87</v>
+      </c>
+      <c r="C20">
+        <v>80</v>
+      </c>
+      <c r="D20">
+        <v>17</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21">
+        <v>29</v>
+      </c>
+      <c r="C21">
+        <v>7</v>
+      </c>
+      <c r="D21">
+        <v>17</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22">
+        <v>37</v>
+      </c>
+      <c r="C22">
+        <v>34</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>34</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24">
+        <v>63</v>
+      </c>
+      <c r="C24">
+        <v>32</v>
+      </c>
+      <c r="D24">
+        <v>5</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25">
+        <v>59</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26">
+        <v>20</v>
+      </c>
+      <c r="C26">
+        <v>40</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27">
+        <v>32</v>
+      </c>
+      <c r="C27">
+        <v>27</v>
+      </c>
+      <c r="D27">
+        <v>19</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28">
+        <v>75</v>
+      </c>
+      <c r="C28">
+        <v>6</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29">
+        <v>57</v>
+      </c>
+      <c r="C29">
+        <v>72</v>
+      </c>
+      <c r="D29">
+        <v>12</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30">
+        <v>21</v>
+      </c>
+      <c r="C30">
+        <v>71</v>
+      </c>
+      <c r="D30">
+        <v>6</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31">
+        <v>88</v>
+      </c>
+      <c r="C31">
+        <v>11</v>
+      </c>
+      <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32">
+        <v>48</v>
+      </c>
+      <c r="C32">
+        <v>33</v>
+      </c>
+      <c r="D32">
+        <v>11</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33">
+        <v>90</v>
+      </c>
+      <c r="C33">
+        <v>32</v>
+      </c>
+      <c r="D33">
+        <v>17</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34">
+        <v>58</v>
+      </c>
+      <c r="C34">
+        <v>47</v>
+      </c>
+      <c r="D34">
+        <v>6</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35">
+        <v>41</v>
+      </c>
+      <c r="C35">
+        <v>22</v>
+      </c>
+      <c r="D35">
+        <v>5</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36">
+        <v>91</v>
+      </c>
+      <c r="C36">
+        <v>61</v>
+      </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37">
+        <v>59</v>
+      </c>
+      <c r="C37">
+        <v>87</v>
+      </c>
+      <c r="D37">
+        <v>6</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38">
+        <v>79</v>
+      </c>
+      <c r="C38">
+        <v>36</v>
+      </c>
+      <c r="D38">
+        <v>11</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39">
+        <v>14</v>
+      </c>
+      <c r="C39">
+        <v>98</v>
+      </c>
+      <c r="D39">
+        <v>16</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40">
+        <v>61</v>
+      </c>
+      <c r="C40">
+        <v>43</v>
+      </c>
+      <c r="D40">
+        <v>16</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41">
+        <v>61</v>
+      </c>
+      <c r="C41">
+        <v>85</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42">
+        <v>46</v>
+      </c>
+      <c r="C42">
+        <v>90</v>
+      </c>
+      <c r="D42">
+        <v>9</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43">
+        <v>61</v>
+      </c>
+      <c r="C43">
+        <v>34</v>
+      </c>
+      <c r="D43">
+        <v>6</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>46</v>
+      </c>
+      <c r="B44">
+        <v>50</v>
+      </c>
+      <c r="C44">
+        <v>64</v>
+      </c>
+      <c r="D44">
+        <v>16</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45">
+        <v>54</v>
+      </c>
+      <c r="C45">
+        <v>98</v>
+      </c>
+      <c r="D45">
+        <v>3</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46">
+        <v>63</v>
+      </c>
+      <c r="C46">
+        <v>46</v>
+      </c>
+      <c r="D46">
+        <v>4</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47">
+        <v>2</v>
+      </c>
+      <c r="C47">
+        <v>77</v>
+      </c>
+      <c r="D47">
+        <v>19</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>50</v>
+      </c>
+      <c r="B48">
+        <v>50</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="D48">
+        <v>3</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>51</v>
+      </c>
+      <c r="B49">
+        <v>6</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>19</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50">
+        <v>20</v>
+      </c>
+      <c r="C50">
+        <v>4</v>
+      </c>
+      <c r="D50">
+        <v>7</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>53</v>
+      </c>
+      <c r="B51">
+        <v>72</v>
+      </c>
+      <c r="C51">
+        <v>89</v>
+      </c>
+      <c r="D51">
+        <v>9</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52">
+        <v>38</v>
+      </c>
+      <c r="C52">
+        <v>13</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53">
+        <v>17</v>
+      </c>
+      <c r="C53">
+        <v>26</v>
+      </c>
+      <c r="D53">
+        <v>8</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54">
+        <v>3</v>
+      </c>
+      <c r="C54">
+        <v>8</v>
+      </c>
+      <c r="D54">
+        <v>7</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>57</v>
+      </c>
+      <c r="B55">
+        <v>88</v>
+      </c>
+      <c r="C55">
+        <v>78</v>
+      </c>
+      <c r="D55">
+        <v>18</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>58</v>
+      </c>
+      <c r="B56">
+        <v>59</v>
+      </c>
+      <c r="C56">
+        <v>14</v>
+      </c>
+      <c r="D56">
+        <v>8</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>59</v>
+      </c>
+      <c r="B57">
+        <v>13</v>
+      </c>
+      <c r="C57">
+        <v>89</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="5"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>60</v>
+      </c>
+      <c r="B58">
+        <v>8</v>
+      </c>
+      <c r="C58">
+        <v>41</v>
+      </c>
+      <c r="D58">
+        <v>11</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="F58" s="5"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="5"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>61</v>
+      </c>
+      <c r="B59">
+        <v>89</v>
+      </c>
+      <c r="C59">
+        <v>76</v>
+      </c>
+      <c r="D59">
+        <v>18</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F59" s="5"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="5"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>62</v>
+      </c>
+      <c r="B60">
+        <v>52</v>
+      </c>
+      <c r="C60">
+        <v>50</v>
+      </c>
+      <c r="D60">
+        <v>10</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F60" s="5"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="5"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>63</v>
+      </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61">
+        <v>62</v>
+      </c>
+      <c r="D61">
+        <v>3</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="F61" s="5"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>64</v>
+      </c>
+      <c r="B62">
+        <v>83</v>
+      </c>
+      <c r="C62">
+        <v>95</v>
+      </c>
+      <c r="D62">
+        <v>7</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F62" s="5"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>65</v>
+      </c>
+      <c r="B63">
+        <v>91</v>
+      </c>
+      <c r="C63">
+        <v>51</v>
+      </c>
+      <c r="D63">
+        <v>16</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>66</v>
+      </c>
+      <c r="B64">
+        <v>59</v>
+      </c>
+      <c r="C64">
+        <v>95</v>
+      </c>
+      <c r="D64">
+        <v>16</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F64" s="5"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>67</v>
+      </c>
+      <c r="B65">
+        <v>70</v>
+      </c>
+      <c r="C65">
+        <v>3</v>
+      </c>
+      <c r="D65">
+        <v>17</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="5"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>68</v>
+      </c>
+      <c r="B66">
+        <v>43</v>
+      </c>
+      <c r="C66">
+        <v>93</v>
+      </c>
+      <c r="D66">
+        <v>2</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>69</v>
+      </c>
+      <c r="B67">
+        <v>7</v>
+      </c>
+      <c r="C67">
+        <v>22</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="F67" s="5"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="5"/>
+      <c r="I67" s="5"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>70</v>
+      </c>
+      <c r="B68">
+        <v>46</v>
+      </c>
+      <c r="C68">
+        <v>14</v>
+      </c>
+      <c r="D68">
+        <v>16</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>71</v>
+      </c>
+      <c r="B69">
+        <v>34</v>
+      </c>
+      <c r="C69">
+        <v>42</v>
+      </c>
+      <c r="D69">
+        <v>12</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="F69" s="5"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
+      <c r="I69" s="5"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>72</v>
+      </c>
+      <c r="B70">
+        <v>77</v>
+      </c>
+      <c r="C70">
+        <v>28</v>
+      </c>
+      <c r="D70">
+        <v>5</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F70" s="5"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>73</v>
+      </c>
+      <c r="B71">
+        <v>80</v>
+      </c>
+      <c r="C71">
+        <v>35</v>
+      </c>
+      <c r="D71">
+        <v>5</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="5"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>74</v>
+      </c>
+      <c r="B72">
+        <v>35</v>
+      </c>
+      <c r="C72">
+        <v>12</v>
+      </c>
+      <c r="D72">
+        <v>9</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>75</v>
+      </c>
+      <c r="B73">
+        <v>49</v>
+      </c>
+      <c r="C73">
+        <v>31</v>
+      </c>
+      <c r="D73">
+        <v>9</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="5"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>76</v>
+      </c>
+      <c r="B74">
+        <v>3</v>
+      </c>
+      <c r="C74">
+        <v>70</v>
+      </c>
+      <c r="D74">
+        <v>3</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>77</v>
+      </c>
+      <c r="B75">
+        <v>1</v>
+      </c>
+      <c r="C75">
+        <v>58</v>
+      </c>
+      <c r="D75">
+        <v>19</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F75" s="5"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="5"/>
+      <c r="I75" s="5"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>78</v>
+      </c>
+      <c r="B76">
+        <v>5</v>
+      </c>
+      <c r="C76">
+        <v>85</v>
+      </c>
+      <c r="D76">
+        <v>16</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="F76" s="5"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="5"/>
+      <c r="I76" s="5"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>79</v>
+      </c>
+      <c r="B77">
+        <v>53</v>
+      </c>
+      <c r="C77">
+        <v>27</v>
+      </c>
+      <c r="D77">
+        <v>16</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="F77" s="5"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5"/>
+      <c r="I77" s="5"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>80</v>
+      </c>
+      <c r="B78">
+        <v>3</v>
+      </c>
+      <c r="C78">
+        <v>65</v>
+      </c>
+      <c r="D78">
+        <v>3</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="F78" s="5"/>
+      <c r="G78" s="5"/>
+      <c r="H78" s="5"/>
+      <c r="I78" s="5"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>81</v>
+      </c>
+      <c r="B79">
+        <v>53</v>
+      </c>
+      <c r="C79">
+        <v>41</v>
+      </c>
+      <c r="D79">
+        <v>1</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F79" s="5"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="5"/>
+      <c r="I79" s="5"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>82</v>
+      </c>
+      <c r="B80">
+        <v>92</v>
+      </c>
+      <c r="C80">
+        <v>44</v>
+      </c>
+      <c r="D80">
+        <v>11</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="F80" s="5"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="5"/>
+      <c r="I80" s="5"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>83</v>
+      </c>
+      <c r="B81">
+        <v>62</v>
+      </c>
+      <c r="C81">
+        <v>61</v>
+      </c>
+      <c r="D81">
+        <v>17</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="F81" s="5"/>
+      <c r="G81" s="5"/>
+      <c r="H81" s="5"/>
+      <c r="I81" s="5"/>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>84</v>
+      </c>
+      <c r="B82">
+        <v>17</v>
+      </c>
+      <c r="C82">
+        <v>56</v>
+      </c>
+      <c r="D82">
+        <v>8</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F82" s="5"/>
+      <c r="G82" s="5"/>
+      <c r="H82" s="5"/>
+      <c r="I82" s="5"/>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>85</v>
+      </c>
+      <c r="B83">
+        <v>89</v>
+      </c>
+      <c r="C83">
+        <v>5</v>
+      </c>
+      <c r="D83">
+        <v>4</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="F83" s="5"/>
+      <c r="G83" s="5"/>
+      <c r="H83" s="5"/>
+      <c r="I83" s="5"/>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>86</v>
+      </c>
+      <c r="B84">
+        <v>43</v>
+      </c>
+      <c r="C84">
+        <v>27</v>
+      </c>
+      <c r="D84">
+        <v>6</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="F84" s="5"/>
+      <c r="G84" s="5"/>
+      <c r="H84" s="5"/>
+      <c r="I84" s="5"/>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>87</v>
+      </c>
+      <c r="B85">
+        <v>33</v>
+      </c>
+      <c r="C85">
+        <v>27</v>
+      </c>
+      <c r="D85">
+        <v>8</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="F85" s="5"/>
+      <c r="G85" s="5"/>
+      <c r="H85" s="5"/>
+      <c r="I85" s="5"/>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>88</v>
+      </c>
+      <c r="B86">
+        <v>73</v>
+      </c>
+      <c r="C86">
+        <v>43</v>
+      </c>
+      <c r="D86">
+        <v>3</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="F86" s="5"/>
+      <c r="G86" s="5"/>
+      <c r="H86" s="5"/>
+      <c r="I86" s="5"/>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>89</v>
+      </c>
+      <c r="B87">
+        <v>61</v>
+      </c>
+      <c r="C87">
+        <v>83</v>
+      </c>
+      <c r="D87">
+        <v>16</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F87" s="5"/>
+      <c r="G87" s="5"/>
+      <c r="H87" s="5"/>
+      <c r="I87" s="5"/>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>90</v>
+      </c>
+      <c r="B88">
+        <v>99</v>
+      </c>
+      <c r="C88">
+        <v>29</v>
+      </c>
+      <c r="D88">
+        <v>3</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="F88" s="5"/>
+      <c r="G88" s="5"/>
+      <c r="H88" s="5"/>
+      <c r="I88" s="5"/>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>91</v>
+      </c>
+      <c r="B89">
+        <v>13</v>
+      </c>
+      <c r="C89">
+        <v>61</v>
+      </c>
+      <c r="D89">
+        <v>18</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="F89" s="5"/>
+      <c r="G89" s="5"/>
+      <c r="H89" s="5"/>
+      <c r="I89" s="5"/>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>92</v>
+      </c>
+      <c r="B90">
+        <v>94</v>
+      </c>
+      <c r="C90">
+        <v>74</v>
+      </c>
+      <c r="D90">
+        <v>14</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F90" s="5"/>
+      <c r="G90" s="5"/>
+      <c r="H90" s="5"/>
+      <c r="I90" s="5"/>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>93</v>
+      </c>
+      <c r="B91">
+        <v>47</v>
+      </c>
+      <c r="C91">
+        <v>91</v>
+      </c>
+      <c r="D91">
+        <v>18</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F91" s="5"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="5"/>
+      <c r="I91" s="5"/>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>94</v>
+      </c>
+      <c r="B92">
+        <v>14</v>
+      </c>
+      <c r="C92">
+        <v>88</v>
+      </c>
+      <c r="D92">
+        <v>2</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F92" s="5"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="5"/>
+      <c r="I92" s="5"/>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>95</v>
+      </c>
+      <c r="B93">
+        <v>71</v>
+      </c>
+      <c r="C93">
+        <v>61</v>
+      </c>
+      <c r="D93">
+        <v>3</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="F93" s="5"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="5"/>
+      <c r="I93" s="5"/>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>96</v>
+      </c>
+      <c r="B94">
+        <v>77</v>
+      </c>
+      <c r="C94">
+        <v>96</v>
+      </c>
+      <c r="D94">
+        <v>16</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="F94" s="5"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="5"/>
+      <c r="I94" s="5"/>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>97</v>
+      </c>
+      <c r="B95">
+        <v>86</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
+      <c r="D95">
+        <v>9</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F95" s="5"/>
+      <c r="G95" s="5"/>
+      <c r="H95" s="5"/>
+      <c r="I95" s="5"/>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>98</v>
+      </c>
+      <c r="B96">
+        <v>61</v>
+      </c>
+      <c r="C96">
+        <v>26</v>
+      </c>
+      <c r="D96">
+        <v>4</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F96" s="5"/>
+      <c r="G96" s="5"/>
+      <c r="H96" s="5"/>
+      <c r="I96" s="5"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>99</v>
+      </c>
+      <c r="B97">
+        <v>39</v>
+      </c>
+      <c r="C97">
+        <v>61</v>
+      </c>
+      <c r="D97">
+        <v>1</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="F97" s="5"/>
+      <c r="G97" s="5"/>
+      <c r="H97" s="5"/>
+      <c r="I97" s="5"/>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>100</v>
+      </c>
+      <c r="B98">
+        <v>84</v>
+      </c>
+      <c r="C98">
+        <v>76</v>
+      </c>
+      <c r="D98">
+        <v>4</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="F98" s="5"/>
+      <c r="G98" s="5"/>
+      <c r="H98" s="5"/>
+      <c r="I98" s="5"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>101</v>
+      </c>
+      <c r="B99">
+        <v>79</v>
+      </c>
+      <c r="C99">
+        <v>2</v>
+      </c>
+      <c r="D99">
+        <v>1</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F99" s="5"/>
+      <c r="G99" s="5"/>
+      <c r="H99" s="5"/>
+      <c r="I99" s="5"/>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>102</v>
+      </c>
+      <c r="B100">
+        <v>81</v>
+      </c>
+      <c r="C100">
+        <v>69</v>
+      </c>
+      <c r="D100">
+        <v>14</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="F100" s="5"/>
+      <c r="G100" s="5"/>
+      <c r="H100" s="5"/>
+      <c r="I100" s="5"/>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>103</v>
+      </c>
+      <c r="B101">
+        <v>52</v>
+      </c>
+      <c r="C101">
+        <v>71</v>
+      </c>
+      <c r="D101">
+        <v>16</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F101" s="5"/>
+      <c r="G101" s="5"/>
+      <c r="H101" s="5"/>
+      <c r="I101" s="5"/>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>104</v>
+      </c>
+      <c r="B102">
+        <v>23</v>
+      </c>
+      <c r="C102">
+        <v>26</v>
+      </c>
+      <c r="D102">
+        <v>8</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F102" s="6"/>
+      <c r="G102" s="6"/>
+      <c r="H102" s="6"/>
+      <c r="I102" s="6"/>
     </row>
   </sheetData>
+  <mergeCells count="101">
+    <mergeCell ref="E100:I100"/>
+    <mergeCell ref="E101:I101"/>
+    <mergeCell ref="E102:I102"/>
+    <mergeCell ref="E94:I94"/>
+    <mergeCell ref="E95:I95"/>
+    <mergeCell ref="E96:I96"/>
+    <mergeCell ref="E97:I97"/>
+    <mergeCell ref="E98:I98"/>
+    <mergeCell ref="E99:I99"/>
+    <mergeCell ref="E88:I88"/>
+    <mergeCell ref="E89:I89"/>
+    <mergeCell ref="E90:I90"/>
+    <mergeCell ref="E91:I91"/>
+    <mergeCell ref="E92:I92"/>
+    <mergeCell ref="E93:I93"/>
+    <mergeCell ref="E82:I82"/>
+    <mergeCell ref="E83:I83"/>
+    <mergeCell ref="E84:I84"/>
+    <mergeCell ref="E85:I85"/>
+    <mergeCell ref="E86:I86"/>
+    <mergeCell ref="E87:I87"/>
+    <mergeCell ref="E76:I76"/>
+    <mergeCell ref="E77:I77"/>
+    <mergeCell ref="E78:I78"/>
+    <mergeCell ref="E79:I79"/>
+    <mergeCell ref="E80:I80"/>
+    <mergeCell ref="E81:I81"/>
+    <mergeCell ref="E70:I70"/>
+    <mergeCell ref="E71:I71"/>
+    <mergeCell ref="E72:I72"/>
+    <mergeCell ref="E73:I73"/>
+    <mergeCell ref="E74:I74"/>
+    <mergeCell ref="E75:I75"/>
+    <mergeCell ref="E64:I64"/>
+    <mergeCell ref="E65:I65"/>
+    <mergeCell ref="E66:I66"/>
+    <mergeCell ref="E67:I67"/>
+    <mergeCell ref="E68:I68"/>
+    <mergeCell ref="E69:I69"/>
+    <mergeCell ref="E58:I58"/>
+    <mergeCell ref="E59:I59"/>
+    <mergeCell ref="E60:I60"/>
+    <mergeCell ref="E61:I61"/>
+    <mergeCell ref="E62:I62"/>
+    <mergeCell ref="E63:I63"/>
+    <mergeCell ref="E52:I52"/>
+    <mergeCell ref="E53:I53"/>
+    <mergeCell ref="E54:I54"/>
+    <mergeCell ref="E55:I55"/>
+    <mergeCell ref="E56:I56"/>
+    <mergeCell ref="E57:I57"/>
+    <mergeCell ref="E46:I46"/>
+    <mergeCell ref="E47:I47"/>
+    <mergeCell ref="E48:I48"/>
+    <mergeCell ref="E49:I49"/>
+    <mergeCell ref="E50:I50"/>
+    <mergeCell ref="E51:I51"/>
+    <mergeCell ref="E40:I40"/>
+    <mergeCell ref="E41:I41"/>
+    <mergeCell ref="E42:I42"/>
+    <mergeCell ref="E43:I43"/>
+    <mergeCell ref="E44:I44"/>
+    <mergeCell ref="E45:I45"/>
+    <mergeCell ref="E34:I34"/>
+    <mergeCell ref="E35:I35"/>
+    <mergeCell ref="E36:I36"/>
+    <mergeCell ref="E37:I37"/>
+    <mergeCell ref="E38:I38"/>
+    <mergeCell ref="E39:I39"/>
+    <mergeCell ref="E28:I28"/>
+    <mergeCell ref="E29:I29"/>
+    <mergeCell ref="E30:I30"/>
+    <mergeCell ref="E31:I31"/>
+    <mergeCell ref="E32:I32"/>
+    <mergeCell ref="E33:I33"/>
+    <mergeCell ref="E22:I22"/>
+    <mergeCell ref="E23:I23"/>
+    <mergeCell ref="E24:I24"/>
+    <mergeCell ref="E25:I25"/>
+    <mergeCell ref="E26:I26"/>
+    <mergeCell ref="E27:I27"/>
+    <mergeCell ref="E16:I16"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="E18:I18"/>
+    <mergeCell ref="E19:I19"/>
+    <mergeCell ref="E20:I20"/>
+    <mergeCell ref="E21:I21"/>
+    <mergeCell ref="E10:I10"/>
+    <mergeCell ref="E11:I11"/>
+    <mergeCell ref="E12:I12"/>
+    <mergeCell ref="E13:I13"/>
+    <mergeCell ref="E14:I14"/>
+    <mergeCell ref="E15:I15"/>
+    <mergeCell ref="E2:I2"/>
+    <mergeCell ref="E3:I3"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="E5:I5"/>
+    <mergeCell ref="E6:I6"/>
+    <mergeCell ref="E7:I7"/>
+    <mergeCell ref="E8:I8"/>
+    <mergeCell ref="E9:I9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>